--- a/output/pdf_financials_xlsx/WN.xlsx
+++ b/output/pdf_financials_xlsx/WN.xlsx
@@ -39837,7 +39837,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>CashEquivalents</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -42027,7 +42027,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>CashEquivalents</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E342" s="5" t="n">
@@ -42328,7 +42328,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>CashEquivalents</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E345" s="5" t="n">

--- a/output/pdf_financials_xlsx/WN.xlsx
+++ b/output/pdf_financials_xlsx/WN.xlsx
@@ -1655,10 +1655,10 @@
         <v>0</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0</v>
+        <v>-322</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
@@ -3908,19 +3908,19 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>0.001145</v>
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0.001296</v>
+        <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>1293</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1555</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>1571</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="n">
         <v>215</v>
@@ -4024,19 +4024,19 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>0.010281</v>
+        <v>0.011426</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.010695</v>
+        <v>0.011991</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>10205</v>
+        <v>11498</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>11036</v>
+        <v>12591</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>11360</v>
+        <v>12931</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>13080</v>
@@ -4579,22 +4579,22 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>4250</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>4242</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>4323</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>4563</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>4977</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>5375</v>
       </c>
     </row>
     <row r="71">
@@ -4637,22 +4637,22 @@
         <v>1579</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1489</v>
+        <v>5739</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>450</v>
+        <v>4692</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>700</v>
+        <v>5023</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>850</v>
+        <v>5413</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>800</v>
+        <v>5777</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>5375</v>
       </c>
     </row>
     <row r="72">
@@ -4869,22 +4869,22 @@
         <v>8025</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>9294</v>
+        <v>5044</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>9323</v>
+        <v>5081</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>10057</v>
+        <v>5734</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>11222</v>
+        <v>6659</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>11722</v>
+        <v>6745</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>14240</v>
+        <v>8865</v>
       </c>
     </row>
     <row r="76">
@@ -5159,22 +5159,22 @@
         <v>1.095043649676148</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>1.077874762808349</v>
+        <v>1.400455407969639</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.9850041866483976</v>
+        <v>1.307908959427571</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>1.069878603945372</v>
+        <v>1.397875569044006</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>1.002079774195944</v>
+        <v>1.341008690485033</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>1.131993605846084</v>
+        <v>1.510847225393926</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>1.006106264869151</v>
+        <v>1.432355273592387</v>
       </c>
     </row>
     <row r="81">
@@ -11325,7 +11325,11 @@
           <t>Lease Liabilities (note 29)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -16892,7 +16896,11 @@
           <t>Lease Liabilities (note 30)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -18183,7 +18191,11 @@
           <t>Lease Liabilities (note 32)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -25613,7 +25625,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -28439,7 +28451,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -31770,7 +31782,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -34681,7 +34693,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E268" s="5" t="n">
@@ -73226,7 +73238,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr"/>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E661" s="5" t="n">
         <v>-1.4e-05</v>
       </c>
@@ -82353,7 +82369,11 @@
           <t>Net Loss from Discontinued Operations</t>
         </is>
       </c>
-      <c r="D756" t="inlineStr"/>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E756" t="inlineStr">
         <is>
           <t>-</t>
@@ -83438,7 +83458,11 @@
           <t>Net Loss from Discontinued Operations</t>
         </is>
       </c>
-      <c r="D767" t="inlineStr"/>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E767" t="inlineStr">
         <is>
           <t>-</t>
@@ -83836,7 +83860,11 @@
           <t>Net Loss from Discontinued Operations (note 7)</t>
         </is>
       </c>
-      <c r="D771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E771" t="inlineStr">
         <is>
           <t>-</t>
@@ -84533,7 +84561,11 @@
           <t>Net Loss from Discontinued Operations (note 7)</t>
         </is>
       </c>
-      <c r="D778" t="inlineStr"/>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E778" t="inlineStr">
         <is>
           <t>-</t>
